--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0060.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0060.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>"Peach"</t>
+          <t>"Đào"</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Zahra</t>
+          <t>Zahira</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sliverglow Bloom</t>
+          <t>Bông Hoa Ánh Bạc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Bướm</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Huafeng</t>
+          <t>Hoa Phong</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Waystone</t>
+          <t>Đá Dẫn Đường</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Contaminated Supply Chest</t>
+          <t>Rương Đồ Bị Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Tony Junior</t>
+          <t>Tony Nhóc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>: "Rage Liberation"</t>
+          <t>: "Giải Phóng Phẫn Nộ"</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Lắng nghe</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Công tắc cửa phòng thí nghiệm Court of Savantae</t>
+          <t>Công tắc cửa Phòng Thí Nghiệm Tòa Savantae</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Lắng nghe</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Temporary Grapple Point Generator</t>
+          <t>Máy Tạo Điểm Treo Tạm Thời</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Liuwen</t>
+          <t>Lục Văn</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Thiết bị Leap</t>
+          <t>Thiết Bị Nhảy Cao</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Serious Acolyte</t>
+          <t>Tín Đồ Nghiêm Túc</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Exile B</t>
+          <t>Kẻ Lưu Đày B</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>: Withering Red</t>
+          <t>: Đỏ Tàn Úa</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Snip Snap: Fire</t>
+          <t>Cắt Xén: Lửa</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Twin Nova: Nebulous Cannon</t>
+          <t>Song Tinh: Đại Bác Vụ Nổ</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Shui</t>
+          <t>Thủy</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Sử dụng điện thoại</t>
+          <t>Dùng điện thoại đi</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Tutorial 1 - Motorbike Driving Techniques</t>
+          <t>Hướng Dẫn 1 - Kỹ Thuật Lái Xe Máy</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>: Severedge</t>
+          <t>: Lưỡi Kiếm Tử Thần</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Thành viên Montelli chán nản</t>
+          <t>Thành viên Montelli u uất</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Enter Sonoro Sphere</t>
+          <t>Vào Sonoro Sphere</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Feilian Beringal: Throwing Stick</t>
+          <t>Feilian Beringal: Gậy Ném</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Serious Patroller</t>
+          <t>Tuần Tra Viên Đứng Đắn</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Rời khỏi Tethys Hệ thống</t>
+          <t>Rời khỏi Hệ Tethys đi</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Quit Interaction</t>
+          <t>Thoát Tương Tác</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Rời khỏi Những Vì Sao</t>
+          <t>Rời khỏi những vì sao đi</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Phagosite: Bipolarch</t>
+          <t>Phagosite: Song Cực Thạch</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Elevator</t>
+          <t>Thang Máy</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Bắt đầu "Mô phỏng Chiến đấu Vô hạn"</t>
+          <t>Bắt đầu "Mô Phỏng Chiến Đấu Vô Tận"</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>: Guardian</t>
+          <t>: Người Bảo Hộ</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Nguyên liệu trong lon</t>
+          <t>Nguyên liệu trong hộp</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Nervous Exile</t>
+          <t>Kẻ Lưu Đày Lo Lắng</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Xuanyin</t>
+          <t>Huyền Âm</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Lấy Chìa khóa Mật mã</t>
+          <t>Lấy Chìa Khóa Mật mã đi</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Panhua's Restaurant</t>
+          <t>Nhà Hàng Panhua</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Giant Soliskin</t>
+          <t>Soliskin Khổng Lồ</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Phantom: Capitaneus</t>
+          <t>Bóng Ma: Capitaneus</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu</t>
+          <t>Nhà Nghiên cứu</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>- Spear of Transgression</t>
+          <t>- Ngọn Giáo Phản Nghịch</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Teeny</t>
+          <t>Nhóc Con</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Tacetite Pollution</t>
+          <t>Ô Nhiễm Tacetite</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Đến Keystone</t>
+          <t>Đến Đá Chìa Khóa ngay</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Tôi muốn nộp Windchimer</t>
+          <t>Tớ muốn nộp Windchimer.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Bắt đầu lại khám phá</t>
+          <t>Bắt đầu lại thám hiểm</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Thử thách Nhận thức III</t>
+          <t>Thử Thách Nhận Thức III</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Choose "Sun"</t>
+          <t>Chọn "Mặt Trời"</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Leave Perspective Bender</t>
+          <t>Rời khỏi Kẻ Bẻ Cong Góc Nhìn</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Công dân biết ơn</t>
+          <t>Công Dân Biết Ơn</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Fractsidus Gunmaster</t>
+          <t>Bậc Thầy Súng Fractsidus</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Nhờ Aemeath giúp vượt qua</t>
+          <t>Nhờ Aemeath giúp cậu vượt qua</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Diggy Duggy</t>
+          <t>Đào Đi Đào Đi</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Move</t>
+          <t>Di Chuyển</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Spectro Drake</t>
+          <t>Drake Spectro</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Dovana</t>
+          <t>Đậu Vana</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Coywood</t>
+          <t>Rừng Coywood</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Roccia Cube</t>
+          <t>Khối lập phương Roccia</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Voidspawn: Ironhoof</t>
+          <t>Voidspawn: Móng Sắt</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Whining Aix's Mire: Đống đổ nát có thể phá hủy B</t>
+          <t>Bãi Lầy Than Vãn của Aix: Tàn Tích Có Thể Phá Hủy B</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Inquire</t>
+          <t>Hỏi thăm</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Explosive Charge</t>
+          <t>Bom nổ</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Nightmare: Impermanence Heron</t>
+          <t>Ác Mộng: Impermanence Heron</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Apple Vendor Beelzbul</t>
+          <t>Beelzbul - Người Bán Táo</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Breen Màn Hình</t>
+          <t>Breen Màn Ảnh</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Royan Bác Sĩ</t>
+          <t>Thầy thuốc Roya</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Leilen</t>
+          <t>Lệ Liên</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Kích hoạt Keystone</t>
+          <t>Kích hoạt Đá Chìa Khóa</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Frostbiter</t>
+          <t>Răng Sương</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Chóng Mặt</t>
+          <t>Nhà Nghiên Cứu Hoa Mắt</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Gulan</t>
+          <t>Gulan...</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Đang Tìm Peep</t>
+          <t>Nhà nghiên cứu Tìm Peep</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Thiên Thạch ở Hồ Linh Hồn</t>
+          <t>Sao Băng Hồ Linh Hồn</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Xiyue</t>
+          <t>Tây Nguyệt</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Khu Vực Thử Thách III</t>
+          <t>Khu vực thử thách III</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Iceglint Dancer</t>
+          <t>Vũ Công Băng Giá</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Icy Clang Bang</t>
+          <t>Âm Thanh Lạnh Lẽo</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ Trăng Đỏ</t>
+          <t>Hiệp Sĩ Trăng Huyết</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Kích hoạt Bộ Phát Lumescribe</t>
+          <t>Kích hoạt Bộ Phát Sáng Lumescribe</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Tidal Supply Chest</t>
+          <t>Rương Cung cấp Thủy Triều</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Tired Fluffguin</t>
+          <t>Chim Cánh Cụt Mệt Phờ</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Sửa chữa</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Sigrika's Diary</t>
+          <t>Nhật ký của Sigrika</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Troubled Courier</t>
+          <t>Người Đưa Thư Lo Lắng</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>: Newborn Desires</t>
+          <t>: Khát Vọng Sơ Sinh</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Exoswarm-herding Youth</t>
+          <t>Thanh niên chăn dắt Exoswarm</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Contaminated Tiêu Chuẩn Supply Chest</t>
+          <t>Rương Đồ Cấp Chuẩn Bị Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Somnoire Only-Snippers</t>
+          <t>Kẻ Chỉ Trích Độc Quyền Somnoire</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Stellar Matrix's Core</t>
+          <t>Lõi Ma Trận Tinh Tú</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Dweller in Dormant Time</t>
+          <t>: Kẻ Ngủ Quên Trong Thời Gian</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Stellar Matrix Navigator</t>
+          <t>Điều Hướng Ma Trận Tinh Tú</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Voidspawn: Flora Reindeer</t>
+          <t>Voidspawn: Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Cosmos</t>
+          <t>Vũ Trụ</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Nghỉ ngơi đi...</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Feed</t>
+          <t>Cho ăn</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Chenyue</t>
+          <t>Thần Nguyệt</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Detonate</t>
+          <t>Kích nổ</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>HA: Detonate</t>
+          <t>HA: Nổ</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Aim On</t>
+          <t>Bật Ngắm</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Aim Off</t>
+          <t>Tắt Ngắm</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Sử dụng khi Điểm Tức Giận xuất hiện</t>
+          <t>Dùng khi Xuất Hiện Điểm Phẫn Nộ</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>BA Bổ Sung</t>
+          <t>BA Thêm</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Sử dụng khi Điểm Tức Giận xuất hiện</t>
+          <t>Dùng khi Xuất Hiện Điểm Phẫn Nộ</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Giữ khi "Mayhem" đầy</t>
+          <t>Giữ khi "Hỗn Loạn" đã đầy</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>HA - Geopotential Shift</t>
+          <t>HA - Dịch Chuyển Địa Thế</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Aerial BA 1</t>
+          <t>BA Trên Không 1</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Aerial BA 2</t>
+          <t>BA Trên Không 2</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Aerial BA 3</t>
+          <t>BA Trên Không 3</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>HA - Inversion</t>
+          <t>HA - Đảo Chiều</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>BA Bổ Sung</t>
+          <t>BA Thêm</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>BA Hit</t>
+          <t>BA Đòn</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>BA Hit</t>
+          <t>BA Đòn</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>BA Hit</t>
+          <t>BA Đòn</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>BA Hit</t>
+          <t>BA Đòn</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Plunging+</t>
+          <t>Đâm Xuống+</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Charge</t>
+          <t>Tấn Công Liên Tiếp</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Charge</t>
+          <t>Tấn Công Liên Tiếp</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Aim</t>
+          <t>Ngắm</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Shoot</t>
+          <t>Bắn</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Shoot</t>
+          <t>Bắn</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Aim Off</t>
+          <t>Tắt Ngắm</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Accumulate Mist Drops</t>
+          <t>Tích lũy Giọt Sương Mù</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Né qua Sương Mù</t>
+          <t>Xuyên qua Sương mù né tránh.</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Phóng trên mặt đất</t>
+          <t>Kích hoạt trên mặt đất</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Phóng giữa không trung</t>
+          <t>Kích hoạt giữa không trung</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Keep Holding</t>
+          <t>Tiếp tục giữ chặt nhé.</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Phóng giữa không trung</t>
+          <t>Kích hoạt giữa không trung</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Có thể phóng giữa không trung</t>
+          <t>Có thể sử dụng khi đang ở trên không</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Thả ra ngay lập tức</t>
+          <t>Thả ngay lập tức</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Lunar Cycle - Half Moon</t>
+          <t>Chu kỳ Mặt Trăng - Trăng Khuyết</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Aftertune</t>
+          <t>Giai Điệu Dư Âm</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Aftertune</t>
+          <t>Giai Điệu Dư Âm</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Air Attack 1</t>
+          <t>Tấn Công Trên Không 1</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Air Attack 2</t>
+          <t>Tấn Công Trên Không 2</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Air Attack 3</t>
+          <t>Tấn Công Trên Không 3</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>HA - Mountain Over Thunder</t>
+          <t>HA - Núi Vượt Sấm</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>HA - Twin Thunders</t>
+          <t>HA - Song Sấm</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Rending Lunge</t>
+          <t>Đòn Lao Xé</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Death Snip</t>
+          <t>Cú Chém Tử Thần</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Death Snip Opening</t>
+          <t>Mở Đầu Cú Chém Tử Thần</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Death Snip Snipping</t>
+          <t>Thực Hiện Cú Chém Tử Thần</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Thread Withdrawn</t>
+          <t>Sợi Dây Rút Lui</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Mid-air HA</t>
+          <t>Tấn Công Trên Không (HA)</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Plunging Attack</t>
+          <t>Tấn Công Đâm Xuống</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Hanging Finality</t>
+          <t>Kết Cục Treo Lơ Lửng</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Lifethread - Glide</t>
+          <t>Sợi Sinh Mệnh - Lướt</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Mid-air Rending Lunge</t>
+          <t>Đòn Lao Tới Xé Rách trên không</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Chainsaw Mode BA 1</t>
+          <t>Chế Độ Cưa Xích BA 1</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Chainsaw Mode BA 2</t>
+          <t>Chế Độ Cưa Xích BA 2</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chainsaw Mode BA 3</t>
+          <t>Chế Độ Cưa Xích BA 3</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chainsaw Mode Finisher</t>
+          <t>Chế Độ Cưa Xích Kết Đòn</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Bắt đầu HA</t>
+          <t>HA Bắt Đầu</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>HA Release</t>
+          <t>HA Giải Phóng</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Bắt đầu HA</t>
+          <t>HA Bắt Đầu</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Enhanced BA</t>
+          <t>BA Nâng Cao</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Air Attack</t>
+          <t>Tấn Công Trên Không</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Ngay lập tức</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Chain Attack</t>
+          <t>Tấn Công Dây Xích</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Né tránh</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Enhanced BA 1</t>
+          <t>BA Nâng Cao 1</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Enhanced BA 2</t>
+          <t>BA Nâng Cao 2</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Enhanced BA 3</t>
+          <t>BA Nâng Cao 3</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Enhanced BA 4</t>
+          <t>BA Nâng Cao 4</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Enhanced BA 5</t>
+          <t>BA Nâng Cao 5</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Giữ Combo</t>
+          <t>Giữ Chuỗi Đòn</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Tiếp tục giữ</t>
+          <t>Tiếp tục giữ vị trí</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>True Sight: Conquest</t>
+          <t>Thị Lực Chân Thật: Chinh Phục</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>True Sight: Charge</t>
+          <t>Thị Lực Chân Thật: Tích Lũy</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Flaming Sacrifice</t>
+          <t>Hy Sinh Lửa Cháy</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Thả</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Charge</t>
+          <t>Tấn Công Liên Tiếp</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>Thả</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Phóng bên ngoài Vòng Gương</t>
+          <t>Kích hoạt bên ngoài Vòng Gương Ảo</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Phóng bên trong Vòng Gương</t>
+          <t>Kích hoạt bên trong Vòng Gương Ảo</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Trảm Nặng Giai Đoạn 1</t>
+          <t>Tấn Công Mạnh Giai Đoạn 1</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Trảm Nặng Giai Đoạn 2</t>
+          <t>Tấn Công Mạnh Giai Đoạn 2</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Trảm Nặng Giai Đoạn 3</t>
+          <t>Cú Chém Nặng Cấp 3</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Heavy Slash Charged</t>
+          <t>Tấn Công Mạnh Tích Lực</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Enhanced BA 3</t>
+          <t>BA Nâng Cao 3</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Plunging Attack</t>
+          <t>Tấn Công Đâm Xuống</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Plunging Chain Attack</t>
+          <t>Chuỗi Tấn Công Đâm Xuống</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Enhanced Mid-air Attack</t>
+          <t>Đòn Tấn Công Giữa Không Nâng Cao</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Enhanced BA</t>
+          <t>BA Nâng Cao</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Chờ Ult kết thúc</t>
+          <t>Đợi Ult kết thúc đã</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Chuyển sang Rover sau đó</t>
+          <t>Sau đó chuyển sang Rover</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Closing Refrain</t>
+          <t>Điệp Khúc Kết</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Lunar Cycle - New Moon</t>
+          <t>Chu kỳ Mặt Trăng - Trăng Non</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 1</t>
+          <t>Vầng Nhật Cao Cả - Hạt Nhân Mặt Trời 1</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 2</t>
+          <t>Vinh Quang Thay - Sunborne 2</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 3</t>
+          <t>Vinh Quang Thay - Sunborne 3</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 4</t>
+          <t>Vinh Quang Thay - Sunborne 4</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 5</t>
+          <t>Vinh Quang Thay - Sunborne 5</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 6</t>
+          <t>Vinh Quang Thay - Sunborne 6</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 7</t>
+          <t>Vinh Quang Thay - Sunborne 7</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 8</t>
+          <t>Vinh Quang Thay - Sunborne 8</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Sunborne 9</t>
+          <t>Vinh Quang Thay - Sunborne 9</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sublime is the Sun - Everbright Protector</t>
+          <t>Vầng Nhật Cao Cả - Người Bảo Vệ Rạng Rỡ</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
